--- a/Result/profitability/3686.xlsx
+++ b/Result/profitability/3686.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
         <v>-0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.10625</v>
+        <v>-0.1275</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -772,7 +772,7 @@
         <v>-2.97</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.485</v>
+        <v>-0.4875</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -885,7 +885,7 @@
         <v>-0.28</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.50875</v>
+        <v>-0.5287500000000001</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -1002,7 +1002,7 @@
         <v>-1.06</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6475000000000001</v>
+        <v>-0.635</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1119,7 +1119,7 @@
         <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6150000000000001</v>
+        <v>-0.61125</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1240,7 +1240,7 @@
         <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.57625</v>
+        <v>-0.56625</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1365,7 +1365,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4825</v>
+        <v>-0.4950000000000001</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -1490,7 +1490,7 @@
         <v>0.89</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3700000000000001</v>
+        <v>-0.37</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
@@ -9542,6 +9542,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3686</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>21</v>
+      </c>
+      <c r="D73" t="n">
+        <v>21</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-29.55%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-0.07999999999999999</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-0.5949999999999982</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="X73" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>-0.4761904761904762</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>-1.602409638554217</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
